--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/MICHIGAN_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/MICHIGAN_2024.xlsx
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C168">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C258">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C370">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C592">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C593">
